--- a/ig/DM-JUIN-2025/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
